--- a/validation_1990_age45/edge_validation.xlsx
+++ b/validation_1990_age45/edge_validation.xlsx
@@ -151,17 +151,19 @@
       </c>
       <c r="G2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The new family study supports familial ADD liability across relatives but supplies no adult age-specific genetic effect; the adult review describes persistence without establishing a genetic cause.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant midlife adult evidence.</t>
+          <t xml:space="preserve">Obtain adult genetic-liability evidence with the relevant phenotype and age scope.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2387786: These results confirm and extend previous findings indicating important family-genetic risk factors in ADD.
+Location: Family-genetic and psychosocial risk factors in DSM-III attention deficit disorder - PubMed.html; English abstract (#eng-abstract)
+Relevance: Blinded family study supports familial liability; shared environment is not fully separated and strong genetic causation or an exact-age effect is not established.</t>
         </is>
       </c>
     </row>
@@ -198,7 +200,7 @@
       </c>
       <c r="G3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="0">
@@ -245,7 +247,7 @@
       </c>
       <c r="G4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="0">
@@ -292,7 +294,7 @@
       </c>
       <c r="G5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr" s="0">
@@ -339,7 +341,7 @@
       </c>
       <c r="G6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="0">
@@ -386,7 +388,7 @@
       </c>
       <c r="G7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr" s="0">
@@ -433,7 +435,7 @@
       </c>
       <c r="G8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="0">
@@ -480,7 +482,7 @@
       </c>
       <c r="G9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="0">
@@ -527,7 +529,7 @@
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr" s="0">
@@ -574,7 +576,7 @@
       </c>
       <c r="G11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr" s="0">
@@ -621,7 +623,7 @@
       </c>
       <c r="G12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr" s="0">
@@ -668,7 +670,7 @@
       </c>
       <c r="G13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr" s="0">
@@ -715,7 +717,7 @@
       </c>
       <c r="G14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr" s="0">
@@ -762,7 +764,7 @@
       </c>
       <c r="G15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr" s="0">
@@ -809,7 +811,7 @@
       </c>
       <c r="G16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="0">
@@ -856,7 +858,7 @@
       </c>
       <c r="G17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr" s="0">
@@ -903,7 +905,7 @@
       </c>
       <c r="G18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="0">
@@ -950,7 +952,7 @@
       </c>
       <c r="G19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr" s="0">
@@ -1091,7 +1093,7 @@
       </c>
       <c r="G22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="0">
@@ -1185,7 +1187,7 @@
       </c>
       <c r="G24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="0">
@@ -1232,7 +1234,7 @@
       </c>
       <c r="G25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr" s="0">
@@ -1279,7 +1281,7 @@
       </c>
       <c r="G26" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr" s="0">
@@ -1326,17 +1328,19 @@
       </c>
       <c r="G27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The new adult review mentions combined psychotherapy and medical management without naming medication or reporting drug-specific outcomes. Pediatric trials cannot supply an adult treatment-effect or medication-uptake estimate.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant midlife adult evidence.</t>
+          <t xml:space="preserve">Obtain adult medication-specific evidence; do not interpret unspecified medical management as a drug trial.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2251528: Once the disorder has been identified in the adult, however, proper intervention with psychotherapy and medical management can make a significant difference in the patient's life.
+Location: Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Adult clinical review supports identification followed by combined care; no controlled estimate, specified medication, behavioral modality, measured quality-of-life outcome, or separate age-32/45 estimate.</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1377,7 @@
       </c>
       <c r="G28" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="0">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="G29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr" s="0">
@@ -1467,7 +1471,7 @@
       </c>
       <c r="G30" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr" s="0">
@@ -1514,7 +1518,7 @@
       </c>
       <c r="G31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr" s="0">
@@ -1561,7 +1565,7 @@
       </c>
       <c r="G32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr" s="0">
@@ -1608,7 +1612,7 @@
       </c>
       <c r="G33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr" s="0">
@@ -1655,7 +1659,7 @@
       </c>
       <c r="G34" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr" s="0">
@@ -1702,7 +1706,7 @@
       </c>
       <c r="G35" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr" s="0">
@@ -1749,17 +1753,19 @@
       </c>
       <c r="G36" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The adult review does not specify behavioral therapy or isolate its effect on functional impairment. Preschool parent training and child medication studies do not establish this adult claim.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant midlife adult evidence.</t>
+          <t xml:space="preserve">Obtain adult behavioral-treatment evidence with separately measured functional outcomes.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2251528: Once the disorder has been identified in the adult, however, proper intervention with psychotherapy and medical management can make a significant difference in the patient's life.
+Location: Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Adult clinical review supports identification followed by combined care; no controlled estimate, specified medication, behavioral modality, measured quality-of-life outcome, or separate age-32/45 estimate.</t>
         </is>
       </c>
     </row>
@@ -1796,17 +1802,19 @@
       </c>
       <c r="G37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The new adult review mentions combined psychotherapy and medical management without naming medication or reporting drug-specific outcomes. Pediatric trials cannot supply an adult treatment-effect or medication-uptake estimate.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant midlife adult evidence.</t>
+          <t xml:space="preserve">Obtain adult medication-specific evidence; do not interpret unspecified medical management as a drug trial.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2251528: Once the disorder has been identified in the adult, however, proper intervention with psychotherapy and medical management can make a significant difference in the patient's life.
+Location: Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Adult clinical review supports identification followed by combined care; no controlled estimate, specified medication, behavioral modality, measured quality-of-life outcome, or separate age-32/45 estimate.</t>
         </is>
       </c>
     </row>
@@ -1843,17 +1851,19 @@
       </c>
       <c r="G38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The new adult review mentions combined psychotherapy and medical management without naming medication or reporting drug-specific outcomes. Pediatric trials cannot supply an adult treatment-effect or medication-uptake estimate.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant midlife adult evidence.</t>
+          <t xml:space="preserve">Obtain adult medication-specific evidence; do not interpret unspecified medical management as a drug trial.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2251528: Once the disorder has been identified in the adult, however, proper intervention with psychotherapy and medical management can make a significant difference in the patient's life.
+Location: Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Adult clinical review supports identification followed by combined care; no controlled estimate, specified medication, behavioral modality, measured quality-of-life outcome, or separate age-32/45 estimate.</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1947,7 @@
       </c>
       <c r="G40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr" s="0">
@@ -1984,7 +1994,7 @@
       </c>
       <c r="G41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr" s="0">
@@ -2031,7 +2041,7 @@
       </c>
       <c r="G42" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr" s="0">
@@ -2078,7 +2088,7 @@
       </c>
       <c r="G43" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr" s="0">
@@ -2120,22 +2130,24 @@
       </c>
       <c r="F44" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The adult review describes identification followed by intervention that can improve life functioning. This partially supports the indirect recognition-to-care pathway, but not an independent effect of diagnosis, measured impairment reduction, or a specific age-45 estimate.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant midlife adult evidence.</t>
+          <t xml:space="preserve">Retain only as an indirect clinical pathway mediated by care; do not claim diagnosis alone reduces impairment.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2251528: Once the disorder has been identified in the adult, however, proper intervention with psychotherapy and medical management can make a significant difference in the patient's life.
+Location: Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Adult clinical review supports identification followed by combined care; no controlled estimate, specified medication, behavioral modality, measured quality-of-life outcome, or separate age-32/45 estimate.</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2184,7 @@
       </c>
       <c r="G45" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The supplied PDFs and HTML abstracts do not establish this specific causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence; the added adult review has no age-45-specific estimate.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr" s="0">
@@ -2219,17 +2231,19 @@
       </c>
       <c r="G46" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The four supplied papers study children or adolescents and do not establish this causal claim for adults around age 45. Pediatric findings are not transferred as midlife evidence.</t>
+          <t xml:space="preserve">The adult review describes making a difference in life following combined care, but does not measure quality of life or isolate a diagnosis-to-quality-of-life effect.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant midlife adult evidence.</t>
+          <t xml:space="preserve">Obtain adult quality-of-life evidence; retain this specific endpoint as unvalidated.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_2251528: Once the disorder has been identified in the adult, however, proper intervention with psychotherapy and medical management can make a significant difference in the patient's life.
+Location: Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html; English abstract (#eng-abstract)
+Relevance: Adult clinical review supports identification followed by combined care; no controlled estimate, specified medication, behavioral modality, measured quality-of-life outcome, or separate age-32/45 estimate.</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2274,7 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Local PDF</t>
+          <t xml:space="preserve">Local file (PDF or HTML)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
@@ -2357,8 +2371,558 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2365665</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">A controlled family history study of Tourette's syndrome, I: Attention-deficit hyperactivity disorder and learning disorders</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/A controlled family history study of Tourette's syndrome, I_ Attention-deficit hyperactivity disorder and learning disorders - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f1f94444f29b5f4673d64acee9d8dcbaf18da10e56b066793e5dd3676018a7bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2289969</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">A critique of current diagnostic criteria for attention deficit hyperactivity disorder: clinical and research implications</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/A critique of current diagnostic criteria for attention deficit hyperactivity disorder_ clinical and research implications - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">218fa32e8a4442796da8f6c55a17d15e743e957e8d002ce7fa4a2fc0018443d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2251528</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention deficit hyperactivity disorder: does it affect adults too?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Attention deficit hyperactivity disorder_ does it affect adults too_ - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f3c844fb24bcf8b0335fd6d1b65ca7f21b316162d3a61e019c07cd2948437bf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="110" customHeight="1">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2326123</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention of hyperactive preschool children--electrodermal activity during auditory stimulation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Attention of hyperactive preschool children--electrodermal activity during auditory stimulation - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">07f5dfbb51849ed390b387078315db9696fcdce856322782bcf9f5638d00f7f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="110" customHeight="1">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_1974836</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention-deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Attention-deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">d8c2c33f0b989dcc71433445922ae7b78df77d6db60b44b52f1e60fa2d02e075</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="110" customHeight="1">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2228924</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Effects of methylphenidate on adolescents with aggressive conduct disorder and ADDH: a preliminary report</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Effects of methylphenidate on adolescents with aggressive conduct disorder and ADDH_ a preliminary report - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">675b6af218f1fe2c234cb340e9ae6b0a1edd38749385786b0593b5f456f5a43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="110" customHeight="1">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2135682</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Efficacy of methylphenidate among mentally retarded children with attention deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Efficacy of methylphenidate among mentally retarded children with attention deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f0a8f9ea45f2211a127fb8ed04b1fde753ee4d18d2726003b34caf303bbd6cc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="110" customHeight="1">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2387786</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Family-genetic and psychosocial risk factors in DSM-III attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Family-genetic and psychosocial risk factors in DSM-III attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">ffa5d6bf3be1d4e2d1b44fa6f1245ac4d424ea5db14bd934a86b2c568c8cfe12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2074343</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Intellectual, academic, and adaptive functioning of Tourette syndrome children with and without attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Intellectual, academic, and adaptive functioning of Tourette syndrome children with and without attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">d93c46b440ae3c249f60f4415df94ae9274f74aab88e6efeaa43f947d3c3c7e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2319047</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Methylphenidate and baseball playing in ADHD children: who's on first?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Methylphenidate and baseball playing in ADHD children_ who's on first_ - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">051e409481456c178ec49ea5487634b325c2949016b85a1e35fb2d23e5437a83</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2228923</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Methylphenidate in aggressive-hyperactive boys: I. Effects on peer aggression in public school settings</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Methylphenidate in aggressive-hyperactive boys_ I. Effects on peer aggression in public school settings - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">b6ef800d54efa3d47c9f62c1f4b02e8910442dcd0756ac1b93b12c1cf45f641a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="110" customHeight="1">
+      <c r="A17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2228921</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Parent-based diagnosis of attention deficit disorder predicts a diagnosis based on teacher report</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Parent-based diagnosis of attention deficit disorder predicts a diagnosis based on teacher report - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">07e69817fb070c372660709f815d0157befb50eb0b7f9021005f16d24ab1ecb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="110" customHeight="1">
+      <c r="A18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2258453</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Possible influence of carbamazepine on plasma imipramine concentrations in children with attention deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Possible influence of carbamazepine on plasma imipramine concentrations in children with attention deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">8c1fdae328b92b0ddca983113718877183b76a26225443e7cc88775f36096515</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="110" customHeight="1">
+      <c r="A19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2196520</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Side effects of methylphenidate in children with attention deficit hyperactivity disorder: a systemic, placebo-controlled evaluation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Side effects of methylphenidate in children with attention deficit hyperactivity disorder_ a systemic, placebo-controlled evaluation - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">ef6d8b034e338e72d2a54ed3031b10f22165595966626567ff8835db3d116221</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2212053</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Situational variability in boys and girls identified as ADHD</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Situational variability in boys and girls identified as ADHD - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">159dfdda96e66c16692acf4f7023c63edf4a329cefeb536d7362cac6b95894b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="110" customHeight="1">
+      <c r="A21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2198308</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Social judgment processes in hyperactive boys: effects of methylphenidate and comparisons with normal peers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/Social judgment processes in hyperactive boys_ effects of methylphenidate and comparisons with normal peers - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">78142ba67858a930b7763d786a0523abcb54deed291a4d36056685029bf8e89f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2254504</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The adolescent outcome of hyperactive children diagnosed by research criteria: II. Academic, attentional, and neuropsychological status</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The adolescent outcome of hyperactive children diagnosed by research criteria_ II. Academic, attentional, and neuropsychological status - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">1a9bd587f2aed3daeb5ae4191acd1d180d4b06a0439a8184e217ee8b3ce26758</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="110" customHeight="1">
+      <c r="A23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2235277</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The diagnostic value of cerebellar-vestibular tests in detecting learning disabilities, dyslexia, and attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The diagnostic value of cerebellar-vestibular tests in detecting learning disabilities, dyslexia, and attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">ecbe1186dd50ba7d2748df6e7182d382580478faeb0b3d338519af40a2f6c7d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="110" customHeight="1">
+      <c r="A24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2273073</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The effects of behavioral parent training on families with young hyperactive children</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The effects of behavioral parent training on families with young hyperactive children - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">67fa8e220f402922cb47b1951b93a76aaa9e93067e44641f90b95d4fb84f343b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="110" customHeight="1">
+      <c r="A25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2266220</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The frequency and significance of additional self-reported psychiatric diagnoses in children with attention deficit disorder</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The frequency and significance of additional self-reported psychiatric diagnoses in children with attention deficit disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">148fdc2bae935e63f4e1dd99221667bf54cf995a7a6d61ed94a2e2e43bd3847c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2342842</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The relationship between continuous performance tasks and neuropsychological tests in children with attention-deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/The relationship between continuous performance tasks and neuropsychological tests in children with attention-deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">44718fa1d74d3f7e7701043ac42b03a0a8adfc2c53d22263688af463752bd3b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="110" customHeight="1">
+      <c r="A27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2288166</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Are there sex differences in the manifestation of hyperkinetic syndrome?]</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[Are there sex differences in the manifestation of hyperkinetic syndrome_] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">4d34da600d22ed8e01e957b81e86cd181494dd0495644d03852f85dbd161c3ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="110" customHeight="1">
+      <c r="A28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2346989</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Changes in the concept of minimal brain dysfunction in modern diagnostic classification and its manifestation in our theory and practice]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[Changes in the concept of minimal brain dysfunction in modern diagnostic classification and its manifestation in our theory and practice] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">eda1f1cf53ae52d2ea482c4d61a1c84d02ecabf5fab93cf902f8179b245d30e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="110" customHeight="1">
+      <c r="A29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2397543</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Preliminary study of traditional Chinese medicine treatment of minimal brain dysfunction: analysis of 100 cases]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[Preliminary study of traditional Chinese medicine treatment of minimal brain dysfunction_ analysis of 100 cases] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">45bc955d755502f0b92d2f2bba322d11c45543b468624948b512dd80419f4cf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="110" customHeight="1">
+      <c r="A30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_2346992</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[The importance of nonverbal motor examination methods in screening for minimal brain dysfunction]</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../1990 ADHD Papers/[The importance of nonverbal motor examination methods in screening for minimal brain dysfunction] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">a9961574979f88c2d3371365599499ac6e7111076b9a75545550443ce1a81a34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:D30"/>
 </worksheet>
 </file>
 
@@ -2389,7 +2953,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">1990_45 yo.py, 58 edges, using only the four supplied PDF files in 1990 ADHD Papers. Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
+          <t xml:space="preserve">1990_45 yo.py, 45 edges, using the four supplied PDF files and 25 saved PubMed HTML abstracts in 1990 ADHD Papers. Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2965,7 @@
       </c>
       <c r="B3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Adult evidence was required for adult claims. The supplied papers study children or adolescents and were not transferred as causal proof for adults aged 45.</t>
+          <t xml:space="preserve">Adult evidence is required for adult claims. The added adult review is treated as partial clinical context without an age-45-specific estimate. Child and adolescent studies are not transferred as adult causal proof.</t>
         </is>
       </c>
     </row>
@@ -2449,83 +3013,107 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No exact duplicate PDF files were found in the supplied corpus.</t>
+          <t xml:space="preserve">No exact duplicate PDFs or duplicate PMID records were found. HTML pages are deduplicated by PMID; repeated sentences in an abstract are not independent findings.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="110" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: supported</t>
+          <t xml:space="preserve">html_scope</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
+          <t xml:space="preserve">HTML evidence is restricted to the main English abstract of each saved record, excluding similar/cited articles. All 25 records are dated 1990. Abstract-only limitations are retained; the side-effect abstract (PMID 2196520) is marked truncated and repeats a passage.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="110" customHeight="1">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: partially_supported</t>
+          <t xml:space="preserve">adult_scope</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
+          <t xml:space="preserve">The adult review (PMID 2251528) supplies clinical context, not a controlled treatment estimate or specific results at age 32 or 45. Pediatric findings are not transferred to adult graphs.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: contradicted</t>
+          <t xml:space="preserve">Status: supported</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
+          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="110" customHeight="1">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: mixed_evidence</t>
+          <t xml:space="preserve">Status: partially_supported</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: insufficient_evidence</t>
+          <t xml:space="preserve">Status: contradicted</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
       <c r="A13" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">Status: mixed_evidence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Status: insufficient_evidence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">Status: not_assessable</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="0">
+      <c r="B15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Undefined variable coding or endpoint makes the proposed direction or sign uninterpretable.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>